--- a/publication/figures/table1_structural.xlsx
+++ b/publication/figures/table1_structural.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table1_v2" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -60,7 +60,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -76,16 +76,11 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
-    <border>
-      <top style="medium">
-        <color rgb="00555555"/>
-      </top>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -93,19 +88,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -477,21 +463,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col hidden="1" width="12" customWidth="1" min="10" max="10"/>
-    <col hidden="1" width="12" customWidth="1" min="11" max="11"/>
-    <col hidden="1" width="12" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col hidden="1" width="12" customWidth="1" min="8" max="8"/>
+    <col hidden="1" width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -502,538 +485,179 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>k</t>
+          <t>Method</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Method</t>
+          <t>SS_RLD (mean)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>SS_RLD (mean)</t>
+          <t>SS_RLD (SD)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>SS_RLD (SD)</t>
+          <t>SS_angle (mean)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>SS_angle (mean)</t>
+          <t>SS_angle (SD)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>SS_angle (SD)</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Chamfer_cm (mean)</t>
+          <t>Best SS_RLD</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Chamfer_cm (SD)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Best SS_RLD</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
           <t>Best SS_angle</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Best Chamfer</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>S2 — elongation known</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+          <t>S2 — elongation known (k=7, 0.2 cm)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>CMA-ES</t>
         </is>
       </c>
+      <c r="C2" s="3" t="n">
+        <v>-0.024</v>
+      </c>
       <c r="D2" s="3" t="n">
-        <v>-0.012</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>0.649</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>0.113</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="I2" s="4" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="J2" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K2" s="4" t="b">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>0.453</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H2" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L2" s="4" t="b">
+      <c r="I2" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>TabICL-MS</t>
         </is>
       </c>
-      <c r="D3" s="4" t="n">
-        <v>-0.183</v>
+      <c r="C3" s="4" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0.91</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>1.453</v>
+        <v>0.393</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>0.314</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="J3" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K3" s="4" t="b">
+        <v>0.375</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H3" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L3" s="4" t="b">
+      <c r="I3" s="3" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>S2 — elongation known</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>S1 — all unknown (k=7, 0.2 cm)</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>CMA-ES</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>0.264</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>0.332</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="J4" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K4" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" s="4" t="b">
+      <c r="C4" s="4" t="n">
+        <v>-0.068</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>-0.139</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="H4" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr"/>
-      <c r="B5" s="2" t="inlineStr"/>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr"/>
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>TabICL-MS</t>
         </is>
       </c>
+      <c r="C5" s="3" t="n">
+        <v>-0.101</v>
+      </c>
       <c r="D5" s="3" t="n">
-        <v>0.226</v>
+        <v>1.195</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.867</v>
+        <v>0.26</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.413</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="J5" s="4" t="b">
+        <v>0.445</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="H5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="b">
         <v>1</v>
-      </c>
-      <c r="K5" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="L5" s="4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>S2 — elongation known</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>CMA-ES</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>0.677</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="J6" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K6" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L6" s="4" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
-      <c r="B7" s="2" t="inlineStr"/>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>TabICL-MS</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>0.336</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>0.591</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>0.462</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>0.358</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="J7" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="L7" s="4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>S1 — all unknown</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>CMA-ES</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>0.773</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="H8" s="7" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="J8" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr"/>
-      <c r="B9" s="8" t="inlineStr"/>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>TabICL-MS</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>-0.369</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>0.276</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>0.389</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J9" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K9" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="L9" s="4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>S1 — all unknown</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>CMA-ES</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>0.632</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>0.398</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="J10" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K10" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr"/>
-      <c r="B11" s="8" t="inlineStr"/>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>TabICL-MS</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>0.109</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>1.007</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>0.343</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="J11" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K11" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="L11" s="4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>S1 — all unknown</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>CMA-ES</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>0.174</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>0.403</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="J12" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K12" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr"/>
-      <c r="B13" s="8" t="inlineStr"/>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>TabICL-MS</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>0.204</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>0.379</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>0.356</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="J13" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K13" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="L13" s="4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>Notes: SS &gt; 0 = better than null predictor. Bold = best per observation condition. N=20 test cases per condition. S2: elongation known (4 arch params calibrated). S1: all 8 params unknown.</t>
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Notes: skin_depth = 0.2 cm (2 mm), k = 7 seeds. SS &gt; 0 = better than null predictor. Bold = best per scenario. S2: elongation known, 4 arch params. S1: all 8 params unknown. S1 N=18 (A_497 and C_100 excluded from S1 calibration).</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A7:G7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/publication/figures/table1_structural.xlsx
+++ b/publication/figures/table1_structural.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table1_v2" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Table1_v2" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>-0.024</v>
+        <v>0.089</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.485</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.101</v>
+        <v>0.065</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.453</v>
+        <v>0.508</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>20</v>
@@ -565,16 +565,16 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.128</v>
+        <v>0.134</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.91</v>
+        <v>0.905</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.393</v>
+        <v>0.417</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.375</v>
+        <v>0.359</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>20</v>
@@ -598,19 +598,19 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>-0.068</v>
+        <v>0.27</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.614</v>
+        <v>0.367</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>-0.139</v>
+        <v>-0.04</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.707</v>
+        <v>0.74</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H4" s="3" t="b">
         <v>1</v>
@@ -627,19 +627,19 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>-0.101</v>
+        <v>-0.018</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1.195</v>
+        <v>1.15</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.26</v>
+        <v>0.298</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.445</v>
+        <v>0.413</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H5" s="3" t="b">
         <v>0</v>
@@ -651,7 +651,7 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Notes: skin_depth = 0.2 cm (2 mm), k = 7 seeds. SS &gt; 0 = better than null predictor. Bold = best per scenario. S2: elongation known, 4 arch params. S1: all 8 params unknown. S1 N=18 (A_497 and C_100 excluded from S1 calibration).</t>
+          <t>Notes: skin_depth = 0.2 cm (2 mm), k = 7 seeds. SS &gt; 0 = better than null predictor. Bold = best per scenario. S2: elongation known, 4 arch params. S1: all 8 params unknown.</t>
         </is>
       </c>
     </row>
